--- a/474/food/tm2026-sm.xlsx
+++ b/474/food/tm2026-sm.xlsx
@@ -1133,7 +1133,7 @@
       </c>
       <c r="H2" s="59" t="inlineStr">
         <is>
-          <t>Муцаев Рамазан Лечиевич</t>
+          <t>Муцаев Рамазан  Лечиевич</t>
         </is>
       </c>
       <c r="I2" s="60" t="n"/>
